--- a/outputs/week2_excel/688775_影石创新_三表抽取.xlsx
+++ b/outputs/week2_excel/688775_影石创新_三表抽取.xlsx
@@ -1832,13 +1832,13 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>张松满</t>
+          <t>孙国奉</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>162.5</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1912,13 +1912,13 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>孙国奉</t>
+          <t>张松满</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>162.5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -2452,15 +2452,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
@@ -2472,7 +2468,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2490,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -2608,11 +2604,15 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2760,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -3102,13 +3102,13 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1584.0</t>
+          <t>7412.0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -3144,13 +3144,13 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1000.0</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -3186,13 +3186,13 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>1584.0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -3228,15 +3228,11 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
@@ -3248,7 +3244,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3270,11 +3266,15 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3308,13 +3308,13 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>7412.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -3392,15 +3392,11 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>中小企业发展基金（深圳有限合伙）</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
@@ -3412,7 +3408,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3434,11 +3430,15 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>中小企业发展基金（深圳有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -3548,15 +3548,11 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>昆山谷捷金属制品有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
@@ -3568,7 +3564,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3586,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -3628,11 +3624,15 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>昆山谷捷金属制品有限公司</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3844,7 +3844,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -4000,11 +4000,15 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>10377.0</t>
+        </is>
+      </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
@@ -4016,7 +4020,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4038,15 +4042,11 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>10377.0</t>
-        </is>
-      </c>
+      <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -4156,7 +4156,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -4958,14 +4958,22 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>上海市青浦县徐泾乡工业公司</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
@@ -4974,7 +4982,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5042,22 +5050,14 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>罗世兵</t>
+          <t>友升太平洋(美国)投资有限公司</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5088,14 +5088,22 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>友升太平洋(美国)投资有限公司</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
@@ -5104,7 +5112,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5126,22 +5134,14 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>上海市青浦县徐泾乡工业公司</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5172,20 +5172,20 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+          <t>罗世兵</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="J107" t="inlineStr"/>
@@ -5218,23 +5218,23 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>2040.0</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -5268,22 +5268,26 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr"/>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
@@ -5292,7 +5296,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5314,26 +5318,22 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>罗世兵</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>408.0</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5364,22 +5364,26 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr"/>
+          <t>上海泽升贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+          <t>8976.0</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>17952.0</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
@@ -5388,7 +5392,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5410,20 +5414,20 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="J112" t="inlineStr"/>
@@ -5456,23 +5460,23 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>罗世兵</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>8976.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>8976.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>17952.0</t>
+          <t>408.0</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -5506,26 +5510,22 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>2040.0</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5556,22 +5556,30 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>86.5984</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>86.5984</t>
-        </is>
-      </c>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>1680.0</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
@@ -5580,7 +5588,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5602,20 +5610,20 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="J116" t="inlineStr"/>
@@ -5694,20 +5702,20 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J118" t="inlineStr"/>
@@ -5740,22 +5748,30 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>10.1093</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>10.1093</t>
-        </is>
-      </c>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>720.0</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
@@ -5764,7 +5780,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5786,30 +5802,22 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>7000.0</t>
-        </is>
-      </c>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>1680.0</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
@@ -5818,7 +5826,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5840,20 +5848,20 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J121" t="inlineStr"/>
@@ -5886,27 +5894,27 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
           <t>360.0</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>720.0</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -5940,20 +5948,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J123" t="inlineStr"/>
@@ -5986,20 +5994,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -6032,20 +6040,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>59.4667</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>59.4667</t>
         </is>
       </c>
       <c r="J125" t="inlineStr"/>
@@ -6078,30 +6086,22 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6132,20 +6132,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="J127" t="inlineStr"/>
@@ -7028,7 +7028,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>华泰大健康一号</t>
+          <t>高新同华</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -7066,7 +7066,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>黄学英/刘鸿雁</t>
+          <t>黄学英</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7104,7 +7104,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>高新同华</t>
+          <t>周乃鼎</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -7120,7 +7120,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>复星惟盈</t>
+          <t>陆民</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
@@ -7156,11 +7156,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7180,7 +7176,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>黄学英</t>
+          <t>华泰大健康一号</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
@@ -7218,7 +7214,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>苏州贤达</t>
+          <t>复星惟盈</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
@@ -7256,7 +7252,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>周乃鼎</t>
+          <t>国寿疌泉</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
@@ -7272,7 +7268,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7294,7 +7290,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>陆民</t>
+          <t>史建伟</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
@@ -7308,7 +7304,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L152" t="inlineStr"/>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>史建伟</t>
+          <t>黄学英/刘鸿雁</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Cheer Rise Consultants Limited</t>
+          <t>周金清</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>周金清</t>
+          <t>Cheer Rise Consultants Limited</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>国寿疌泉</t>
+          <t>苏州贤达</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>深圳中证投资有限责任公司</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -7556,7 +7556,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -7632,7 +7632,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -7708,7 +7708,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>厦门富凯海创投资管理有限责任公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>深圳中证投资有限责任公司</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -7784,7 +7784,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>厦门富凯海创投资管理有限责任公司</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -7822,7 +7822,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -7898,11 +7898,15 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
@@ -7912,11 +7916,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -7936,15 +7936,11 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F169" t="inlineStr"/>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr"/>
@@ -7954,7 +7950,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L169" t="inlineStr"/>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -7974,7 +7974,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -8012,7 +8012,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -8088,7 +8088,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
@@ -8328,15 +8328,11 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>吴功友(王金林代持)</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
+      <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr"/>
@@ -8348,7 +8344,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8370,7 +8366,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -8408,13 +8404,13 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>四方股份</t>
+          <t>吴功友(王金林代持)</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
-          <t>1200.0</t>
+          <t>400.0</t>
         </is>
       </c>
       <c r="G181" t="inlineStr"/>
@@ -8450,11 +8446,15 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>四方股份</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr"/>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8530,20 +8530,20 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>策星揽月</t>
+          <t>幸福二期</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr"/>
       <c r="G184" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="J184" t="inlineStr"/>
@@ -8618,20 +8618,20 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司</t>
+          <t>策星九天</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr">
         <is>
-          <t>3825.0</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr">
         <is>
-          <t>3825.0</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="J186" t="inlineStr"/>
@@ -8664,20 +8664,20 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>策星九天</t>
+          <t>中科星图股份有限公司</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="J187" t="inlineStr"/>
@@ -8752,20 +8752,20 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>幸福一期</t>
+          <t>策星揽月</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="J189" t="inlineStr"/>
@@ -8798,20 +8798,20 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>策星银河</t>
+          <t>幸福一期</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr"/>
       <c r="G190" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="J190" t="inlineStr"/>
@@ -8844,20 +8844,20 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>幸福二期</t>
+          <t>策星银河</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="J191" t="inlineStr"/>
@@ -9285,7 +9285,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>生成时间: 2026-06-12T10:04:41.122547</t>
+          <t>生成时间: 2026-06-12T14:44:15.889505</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/688775_影石创新_三表抽取.xlsx
+++ b/outputs/week2_excel/688775_影石创新_三表抽取.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -452,7 +452,10 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -488,6 +491,21 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>事件类型</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>增资后总股本(万股)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>认购占比</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>原文证据</t>
         </is>
       </c>
@@ -513,6 +531,16 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>2015年7月9日，北京岚锋以货币出资方式设立深圳岚锋，公司注册资本1,000.00万元。深圳岚锋设立时，股东情况为：北京岚锋100%。</t>
         </is>
       </c>
@@ -535,6 +563,16 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>VIE搭建</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>13.32%</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>容诚验字[2020]518Z0004号验证：有限公司阶段完成了设立及六次增资扩股。股改时注册资本9,718.8612万元。公司曾搭建境外VIE架构（开曼岚锋-Huahua控股-Lancefield控股-香港岚锋-北京WFOE），后为境内上市拆除。投资方包括IDG（EARN ACE/QM101）、启明创投、迅雷、苏宁（伊敦传媒）、华金同达等。</t>
         </is>
       </c>
@@ -557,6 +595,16 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>VIE搭建</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>9.40%</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>容诚验字[2020]518Z0004号验证：有限公司阶段完成了设立及六次增资扩股。股改时注册资本9,718.8612万元。公司曾搭建境外VIE架构（开曼岚锋-Huahua控股-Lancefield控股-香港岚锋-北京WFOE），后为境内上市拆除。投资方包括IDG（EARN ACE/QM101）、启明创投、迅雷、苏宁（伊敦传媒）、华金同达等。</t>
         </is>
       </c>
@@ -579,6 +627,16 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>VIE搭建</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>8.73%</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>容诚验字[2020]518Z0004号验证：有限公司阶段完成了设立及六次增资扩股。股改时注册资本9,718.8612万元。公司曾搭建境外VIE架构（开曼岚锋-Huahua控股-Lancefield控股-香港岚锋-北京WFOE），后为境内上市拆除。投资方包括IDG（EARN ACE/QM101）、启明创投、迅雷、苏宁（伊敦传媒）、华金同达等。</t>
         </is>
       </c>
@@ -601,6 +659,16 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>VIE搭建</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3.70%</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>容诚验字[2020]518Z0004号验证：有限公司阶段完成了设立及六次增资扩股。股改时注册资本9,718.8612万元。公司曾搭建境外VIE架构（开曼岚锋-Huahua控股-Lancefield控股-香港岚锋-北京WFOE），后为境内上市拆除。投资方包括IDG（EARN ACE/QM101）、启明创投、迅雷、苏宁（伊敦传媒）、华金同达等。</t>
         </is>
       </c>
@@ -623,6 +691,16 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>VIE搭建</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2.71%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>容诚验字[2020]518Z0004号验证：有限公司阶段完成了设立及六次增资扩股。股改时注册资本9,718.8612万元。公司曾搭建境外VIE架构（开曼岚锋-Huahua控股-Lancefield控股-香港岚锋-北京WFOE），后为境内上市拆除。投资方包括IDG（EARN ACE/QM101）、启明创投、迅雷、苏宁（伊敦传媒）、华金同达等。</t>
         </is>
       </c>
@@ -645,6 +723,16 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>VIE搭建</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3.99%</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>容诚验字[2020]518Z0004号验证：有限公司阶段完成了设立及六次增资扩股。股改时注册资本9,718.8612万元。公司曾搭建境外VIE架构（开曼岚锋-Huahua控股-Lancefield控股-香港岚锋-北京WFOE），后为境内上市拆除。投资方包括IDG（EARN ACE/QM101）、启明创投、迅雷、苏宁（伊敦传媒）、华金同达等。</t>
         </is>
       </c>
@@ -667,6 +755,16 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>VIE搭建</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2.53%</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>容诚验字[2020]518Z0004号验证：有限公司阶段完成了设立及六次增资扩股。股改时注册资本9,718.8612万元。公司曾搭建境外VIE架构（开曼岚锋-Huahua控股-Lancefield控股-香港岚锋-北京WFOE），后为境内上市拆除。投资方包括IDG（EARN ACE/QM101）、启明创投、迅雷、苏宁（伊敦传媒）、华金同达等。</t>
         </is>
       </c>
@@ -689,6 +787,16 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>VIE搭建</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2.53%</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>容诚验字[2020]518Z0004号验证：有限公司阶段完成了设立及六次增资扩股。股改时注册资本9,718.8612万元。公司曾搭建境外VIE架构（开曼岚锋-Huahua控股-Lancefield控股-香港岚锋-北京WFOE），后为境内上市拆除。投资方包括IDG（EARN ACE/QM101）、启明创投、迅雷、苏宁（伊敦传媒）、华金同达等。</t>
         </is>
       </c>
@@ -711,6 +819,16 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>29.94%</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>截至2019年10月31日，深圳岚锋账面净资产52,728.05万元。全体股东以其拥有的净资产52,728.05万元出资，按1:1.4647比例折合股本36,000.00万元，其余计入资本公积。2020年2月26日，深圳市市场监督管理局核准。股改后27名股东，北京岚锋29.9376%、EARN ACE 13.3239%、QM101 9.4001%、香港迅雷8.7327%等。</t>
         </is>
       </c>
@@ -733,6 +851,16 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>13.32%</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>截至2019年10月31日，深圳岚锋账面净资产52,728.05万元。全体股东以其拥有的净资产52,728.05万元出资，按1:1.4647比例折合股本36,000.00万元，其余计入资本公积。2020年2月26日，深圳市市场监督管理局核准。股改后27名股东，北京岚锋29.9376%、EARN ACE 13.3239%、QM101 9.4001%、香港迅雷8.7327%等。</t>
         </is>
       </c>
@@ -755,6 +883,16 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>9.40%</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>截至2019年10月31日，深圳岚锋账面净资产52,728.05万元。全体股东以其拥有的净资产52,728.05万元出资，按1:1.4647比例折合股本36,000.00万元，其余计入资本公积。2020年2月26日，深圳市市场监督管理局核准。股改后27名股东，北京岚锋29.9376%、EARN ACE 13.3239%、QM101 9.4001%、香港迅雷8.7327%等。</t>
         </is>
       </c>
@@ -777,6 +915,16 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>8.73%</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>截至2019年10月31日，深圳岚锋账面净资产52,728.05万元。全体股东以其拥有的净资产52,728.05万元出资，按1:1.4647比例折合股本36,000.00万元，其余计入资本公积。2020年2月26日，深圳市市场监督管理局核准。股改后27名股东，北京岚锋29.9376%、EARN ACE 13.3239%、QM101 9.4001%、香港迅雷8.7327%等。</t>
         </is>
       </c>
@@ -804,6 +952,16 @@
         <v>5.096</v>
       </c>
       <c r="G15" t="inlineStr">
+        <is>
+          <t>股权转让</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1.33%</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>2023年1月28日和2023年2月17日，影石创新分别召开董事会和股东大会，同意德朴投资以1,462.7126万元的对价向汇智同裕转让股本287.0651万元。2023年3月24日，深圳市市场监督管理局核准。汇智同裕持股从0.5321%增至1.3295%，德朴投资完全退出。</t>
         </is>
@@ -820,7 +978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -832,7 +990,10 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -883,6 +1044,21 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>快照序号</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>股东类型</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>原始创始人</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>原文证据</t>
         </is>
       </c>
@@ -918,6 +1094,21 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>2015年7月9日，北京岚锋以货币出资方式设立深圳岚锋，公司注册资本1,000.00万元。深圳岚锋设立时，股东情况为：北京岚锋100%。</t>
         </is>
       </c>
@@ -950,6 +1141,21 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
           <t>容诚验字[2020]518Z0004号验证：有限公司阶段完成了设立及六次增资扩股。股改时注册资本9,718.8612万元。公司曾搭建境外VIE架构（开曼岚锋-Huahua控股-Lancefield控股-香港岚锋-北京WFOE），后为境内上市拆除。投资方包括IDG（EARN ACE/QM101）、启明创投、迅雷、苏宁（伊敦传媒）、华金同达等。</t>
         </is>
       </c>
@@ -982,6 +1188,21 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>外部VC</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>容诚验字[2020]518Z0004号验证：有限公司阶段完成了设立及六次增资扩股。股改时注册资本9,718.8612万元。公司曾搭建境外VIE架构（开曼岚锋-Huahua控股-Lancefield控股-香港岚锋-北京WFOE），后为境内上市拆除。投资方包括IDG（EARN ACE/QM101）、启明创投、迅雷、苏宁（伊敦传媒）、华金同达等。</t>
         </is>
       </c>
@@ -1014,6 +1235,21 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>产业资本</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
           <t>容诚验字[2020]518Z0004号验证：有限公司阶段完成了设立及六次增资扩股。股改时注册资本9,718.8612万元。公司曾搭建境外VIE架构（开曼岚锋-Huahua控股-Lancefield控股-香港岚锋-北京WFOE），后为境内上市拆除。投资方包括IDG（EARN ACE/QM101）、启明创投、迅雷、苏宁（伊敦传媒）、华金同达等。</t>
         </is>
       </c>
@@ -1046,6 +1282,21 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
           <t>容诚验字[2020]518Z0004号验证：有限公司阶段完成了设立及六次增资扩股。股改时注册资本9,718.8612万元。公司曾搭建境外VIE架构（开曼岚锋-Huahua控股-Lancefield控股-香港岚锋-北京WFOE），后为境内上市拆除。投资方包括IDG（EARN ACE/QM101）、启明创投、迅雷、苏宁（伊敦传媒）、华金同达等。</t>
         </is>
       </c>
@@ -1078,6 +1329,21 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
           <t>容诚验字[2020]518Z0004号验证：有限公司阶段完成了设立及六次增资扩股。股改时注册资本9,718.8612万元。公司曾搭建境外VIE架构（开曼岚锋-Huahua控股-Lancefield控股-香港岚锋-北京WFOE），后为境内上市拆除。投资方包括IDG（EARN ACE/QM101）、启明创投、迅雷、苏宁（伊敦传媒）、华金同达等。</t>
         </is>
       </c>
@@ -1110,6 +1376,21 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
           <t>容诚验字[2020]518Z0004号验证：有限公司阶段完成了设立及六次增资扩股。股改时注册资本9,718.8612万元。公司曾搭建境外VIE架构（开曼岚锋-Huahua控股-Lancefield控股-香港岚锋-北京WFOE），后为境内上市拆除。投资方包括IDG（EARN ACE/QM101）、启明创投、迅雷、苏宁（伊敦传媒）、华金同达等。</t>
         </is>
       </c>
@@ -1142,6 +1423,21 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
           <t>容诚验字[2020]518Z0004号验证：有限公司阶段完成了设立及六次增资扩股。股改时注册资本9,718.8612万元。公司曾搭建境外VIE架构（开曼岚锋-Huahua控股-Lancefield控股-香港岚锋-北京WFOE），后为境内上市拆除。投资方包括IDG（EARN ACE/QM101）、启明创投、迅雷、苏宁（伊敦传媒）、华金同达等。</t>
         </is>
       </c>
@@ -1174,6 +1470,21 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
           <t>容诚验字[2020]518Z0004号验证：有限公司阶段完成了设立及六次增资扩股。股改时注册资本9,718.8612万元。公司曾搭建境外VIE架构（开曼岚锋-Huahua控股-Lancefield控股-香港岚锋-北京WFOE），后为境内上市拆除。投资方包括IDG（EARN ACE/QM101）、启明创投、迅雷、苏宁（伊敦传媒）、华金同达等。</t>
         </is>
       </c>
@@ -1206,6 +1517,21 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
           <t>截至2019年10月31日，深圳岚锋账面净资产52,728.05万元。全体股东以其拥有的净资产52,728.05万元出资，按1:1.4647比例折合股本36,000.00万元，其余计入资本公积。2020年2月26日，深圳市市场监督管理局核准。股改后27名股东，北京岚锋29.9376%、EARN ACE 13.3239%、QM101 9.4001%、香港迅雷8.7327%等。</t>
         </is>
       </c>
@@ -1238,6 +1564,21 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
           <t>截至2019年10月31日，深圳岚锋账面净资产52,728.05万元。全体股东以其拥有的净资产52,728.05万元出资，按1:1.4647比例折合股本36,000.00万元，其余计入资本公积。2020年2月26日，深圳市市场监督管理局核准。股改后27名股东，北京岚锋29.9376%、EARN ACE 13.3239%、QM101 9.4001%、香港迅雷8.7327%等。</t>
         </is>
       </c>
@@ -1270,6 +1611,21 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>外部VC</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
           <t>截至2019年10月31日，深圳岚锋账面净资产52,728.05万元。全体股东以其拥有的净资产52,728.05万元出资，按1:1.4647比例折合股本36,000.00万元，其余计入资本公积。2020年2月26日，深圳市市场监督管理局核准。股改后27名股东，北京岚锋29.9376%、EARN ACE 13.3239%、QM101 9.4001%、香港迅雷8.7327%等。</t>
         </is>
       </c>
@@ -1302,6 +1658,21 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>产业资本</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
           <t>截至2019年10月31日，深圳岚锋账面净资产52,728.05万元。全体股东以其拥有的净资产52,728.05万元出资，按1:1.4647比例折合股本36,000.00万元，其余计入资本公积。2020年2月26日，深圳市市场监督管理局核准。股改后27名股东，北京岚锋29.9376%、EARN ACE 13.3239%、QM101 9.4001%、香港迅雷8.7327%等。</t>
         </is>
       </c>
@@ -1336,6 +1707,21 @@
         </is>
       </c>
       <c r="J15" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
         <is>
           <t>2023年1月28日和2023年2月17日，影石创新分别召开董事会和股东大会，同意德朴投资以1,462.7126万元的对价向汇智同裕转让股本287.0651万元。2023年3月24日，深圳市市场监督管理局核准。汇智同裕持股从0.5321%增至1.3295%，德朴投资完全退出。</t>
         </is>
@@ -1352,7 +1738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L203"/>
+  <dimension ref="A1:L211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1526,100 +1912,84 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>evidence_text</t>
+          <t>event_context</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>str(min=20)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>equity_snapshot</t>
+          <t>subscription_flow</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>source_page</t>
+          <t>post_event_total_shares</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>float|null</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>equity_snapshot</t>
+          <t>subscription_flow</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>snapshot_date</t>
+          <t>post_event_total_capital</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>str(YYYY-MM-DD)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>float|null</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>equity_snapshot</t>
+          <t>subscription_flow</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>snapshot_type</t>
+          <t>payment_method</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>equity_snapshot</t>
+          <t>subscription_flow</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>total_shares</t>
+          <t>subscription_ratio</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>float|null</t>
+          <t>str|null</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -1627,20 +1997,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>equity_snapshot</t>
+          <t>subscription_flow</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>total_capital</t>
+          <t>evidence_text</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>float|null</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>str(min=20)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1650,7 +2024,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>shareholder_name</t>
+          <t>source_page</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1672,15 +2046,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>shares_held</t>
+          <t>snapshot_date</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>float|null</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>str(YYYY-MM-DD)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1690,15 +2068,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>capital_contribution</t>
+          <t>snapshot_type</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>float|null</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1708,12 +2090,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>shareholding_ratio</t>
+          <t>total_shares</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>str|null</t>
+          <t>float|null</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1726,433 +2108,269 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>total_capital</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>float|null</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>shareholder_name</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>shares_held</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>float|null</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>capital_contribution</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>float|null</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>shareholding_ratio</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>str|null</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>snapshot_order</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>int|null</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>shareholder_type_detail</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>is_original_founder</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>yes/no/unknown</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>evidence_text</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>str(min=20)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Cross-Check 结果（相邻时点股本追踪 + 认缴存量对应）</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
         <is>
           <t>公司</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
+      <c r="B32" s="1" t="inlineStr">
         <is>
           <t>上一时点</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>当前时点</t>
         </is>
       </c>
-      <c r="D24" s="1" t="inlineStr">
+      <c r="D32" s="1" t="inlineStr">
         <is>
           <t>股东名称</t>
         </is>
       </c>
-      <c r="E24" s="1" t="inlineStr">
+      <c r="E32" s="1" t="inlineStr">
         <is>
           <t>上一时点持股数
 (万股)</t>
         </is>
       </c>
-      <c r="F24" s="1" t="inlineStr">
+      <c r="F32" s="1" t="inlineStr">
         <is>
           <t>上一时点出资额
 (万元注册资本)</t>
         </is>
       </c>
-      <c r="G24" s="1" t="inlineStr">
+      <c r="G32" s="1" t="inlineStr">
         <is>
           <t>本次认缴/变化
 (万股)</t>
         </is>
       </c>
-      <c r="H24" s="1" t="inlineStr">
+      <c r="H32" s="1" t="inlineStr">
         <is>
           <t>预期变更后
 持股数(万股)</t>
         </is>
       </c>
-      <c r="I24" s="1" t="inlineStr">
+      <c r="I32" s="1" t="inlineStr">
         <is>
           <t>PDF披露
 持股数(万股)</t>
         </is>
       </c>
-      <c r="J24" s="1" t="inlineStr">
+      <c r="J32" s="1" t="inlineStr">
         <is>
           <t>差额(万股)</t>
         </is>
       </c>
-      <c r="K24" s="1" t="inlineStr">
+      <c r="K32" s="1" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="L24" s="1" t="inlineStr">
+      <c r="L32" s="1" t="inlineStr">
         <is>
           <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>001282_三联锻造</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2004-06-18</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2014-05</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>孙国奉</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>175.0</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>001282_三联锻造</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2004-06-18</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>2014-05</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>孙国敏</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>162.5</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>001282_三联锻造</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2004-06-18</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2014-05</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>张松满</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>162.5</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>301563_云汉芯城</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2008-05-07</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>武汉力源信息技术股份有限公司</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>301563_云汉芯城</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2008-05-07</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>301563_云汉芯城</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2008-05-07</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>深圳市云汉电子有限公司</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>301563_云汉芯城</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2008-05-07</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>刘云锋</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>301563_云汉芯城</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2008-05-07</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>301563_云汉芯城</t>
+          <t>001282_三联锻造</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2004-06-18</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2015-08</t>
+          <t>2014-05</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>孙国奉</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>175.0</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
@@ -2162,35 +2380,35 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>301563_云汉芯城</t>
+          <t>001282_三联锻造</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2004-06-18</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2015-08</t>
+          <t>2014-05</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>张松满</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>162.5</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
@@ -2200,35 +2418,35 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>301563_云汉芯城</t>
+          <t>001282_三联锻造</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2004-06-18</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2015-08</t>
+          <t>2014-05</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>孙国敏</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>162.5</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
@@ -2240,7 +2458,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2252,17 +2470,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>2008-05-07</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>2014-08</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -2290,21 +2508,25 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>2008-05-07</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
           <t>2014-08</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
@@ -2328,21 +2550,25 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>2008-05-07</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>2014-08</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>深圳市云汉电子有限公司</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
@@ -2354,7 +2580,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2366,17 +2592,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>2008-05-07</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>2014-08</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -2392,7 +2618,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2404,17 +2630,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>2008-05-07</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
           <t>2014-08</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -2442,17 +2668,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -2468,7 +2694,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2480,17 +2706,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -2518,17 +2744,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -2544,7 +2770,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2556,17 +2782,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -2582,7 +2808,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2594,25 +2820,21 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -2624,7 +2846,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2636,17 +2858,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -2662,7 +2884,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2674,17 +2896,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -2700,7 +2922,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2712,17 +2934,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2750,17 +2972,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -2788,17 +3010,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2814,7 +3036,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2826,21 +3048,25 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
@@ -2852,7 +3078,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2864,17 +3090,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -2902,17 +3128,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -2940,17 +3166,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -2966,7 +3192,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2978,17 +3204,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -3016,17 +3242,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -3042,7 +3268,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3290,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -3080,7 +3306,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3092,25 +3318,21 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>7412.0</t>
-        </is>
-      </c>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
@@ -3122,7 +3344,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3134,25 +3356,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
@@ -3176,25 +3394,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>1584.0</t>
-        </is>
-      </c>
+      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
@@ -3206,7 +3420,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3218,17 +3432,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -3256,25 +3470,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D62" t="inlineStr">
         <is>
           <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
@@ -3286,7 +3496,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3298,25 +3508,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
@@ -3328,7 +3534,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3340,25 +3546,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -3370,7 +3572,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3382,17 +3584,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2020-05-28</t>
+          <t>2015-12-03</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>中小企业发展基金（深圳有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -3408,7 +3610,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3420,25 +3622,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
+          <t>2018-06-28</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
           <t>2020-05-28</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>2020-09-23</t>
-        </is>
-      </c>
       <c r="D66" t="inlineStr">
         <is>
           <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
@@ -3450,7 +3648,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3462,21 +3660,25 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
+          <t>2018-06-28</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
           <t>2020-05-28</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>2020-09-23</t>
-        </is>
-      </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
@@ -3488,33 +3690,37 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2012-06-12</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
@@ -3526,33 +3732,37 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2012-06-12</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>7412.0</t>
+        </is>
+      </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
@@ -3564,33 +3774,37 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2012-06-12</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
@@ -3602,35 +3816,35 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2012-06-12</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>昆山谷捷金属制品有限公司</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -3651,26 +3865,30 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>1584.0</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
@@ -3680,31 +3898,39 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -3714,27 +3940,31 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -3748,27 +3978,31 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>中小企业发展基金（深圳有限合伙）</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -3784,7 +4018,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3796,12 +4030,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2012-06-12</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3822,7 +4056,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3834,17 +4068,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2012-06-12</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -3872,17 +4106,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2012-06-12</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -3910,21 +4144,25 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2012-06-12</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>昆山谷捷金属制品有限公司</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -3948,25 +4186,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>1153.0</t>
-        </is>
-      </c>
+      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
@@ -3976,11 +4210,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3990,25 +4220,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>10377.0</t>
-        </is>
-      </c>
+      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
@@ -4018,11 +4244,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4032,17 +4254,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -4056,11 +4278,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4070,17 +4288,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -4096,7 +4314,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4108,12 +4326,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4134,7 +4352,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4146,12 +4364,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4184,12 +4402,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4222,25 +4440,21 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2124.81</t>
-        </is>
-      </c>
+      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
@@ -4250,7 +4464,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4260,21 +4478,25 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
           <t>2022-05-26</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>2022-09-13</t>
-        </is>
-      </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>1153.0</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
@@ -4286,49 +4508,37 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-05-26</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>6999.972</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>7000.0</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>-0.028</t>
-        </is>
-      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4336,49 +4546,41 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-05-26</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>2999.988</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>-0.012</t>
-        </is>
-      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>10377.0</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4386,49 +4588,37 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>1499.994</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>-0.006</t>
-        </is>
-      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4436,49 +4626,37 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>10000.0027</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>10000.0</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>0.0027</t>
-        </is>
-      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4486,49 +4664,37 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>10000.0027</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>10000.0</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>0.0027</t>
-        </is>
-      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4536,99 +4702,75 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>148.6667</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>5000.0031</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>0.0031</t>
-        </is>
-      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2124.81</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>price×shares vs amount diff=0.0%</t>
-        </is>
-      </c>
+      <c r="L94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>3000.0012</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>0.0012</t>
-        </is>
-      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4636,49 +4778,37 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>86.5984</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>2912.5034</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>2912.5</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>0.0034</t>
-        </is>
-      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4686,7 +4816,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4699,34 +4829,34 @@
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2000.0019</t>
+          <t>6999.972</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>7000.0</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>0.0019</t>
+          <t>-0.028</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -4749,34 +4879,34 @@
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>1747.5007</t>
+          <t>2999.988</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>1747.5</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>0.0007</t>
+          <t>-0.012</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -4799,34 +4929,34 @@
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>999.9993</t>
+          <t>1499.994</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>1500.0</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>-0.0007</t>
+          <t>-0.006</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -4854,29 +4984,29 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>999.9993</t>
+          <t>10000.0027</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>10000.0</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>-0.0007</t>
+          <t>0.0027</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -4904,29 +5034,29 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>339.999</t>
+          <t>10000.0027</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>340.0</t>
+          <t>10000.0</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>0.0027</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -4946,35 +5076,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr"/>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>5000.0031</t>
+        </is>
+      </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr"/>
+          <t>5000.0</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>0.0031</t>
+        </is>
+      </c>
       <c r="K102" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4982,7 +5116,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -4992,35 +5126,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr"/>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>3000.0012</t>
+        </is>
+      </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr"/>
+          <t>3000.0</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>0.0012</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5028,7 +5166,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5038,27 +5176,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>友升太平洋(美国)投资有限公司</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2912.5034</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2912.5</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>0.0034</t>
+        </is>
+      </c>
       <c r="K104" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5066,7 +5216,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5076,35 +5226,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr"/>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2000.0019</t>
+        </is>
+      </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr"/>
+          <t>2000.0</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>0.0019</t>
+        </is>
+      </c>
       <c r="K105" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5112,7 +5266,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5122,27 +5276,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>上海市青浦县徐泾乡工业公司</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>1747.5007</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>1747.5</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>0.0007</t>
+        </is>
+      </c>
       <c r="K106" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5150,7 +5316,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5160,35 +5326,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>罗世兵</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr"/>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>999.9993</t>
+        </is>
+      </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr"/>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>-0.0007</t>
+        </is>
+      </c>
       <c r="K107" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5196,7 +5366,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5206,39 +5376,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>2020-09-09</t>
-        </is>
-      </c>
+      <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2040.0</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
+          <t>999.9993</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>-0.0007</t>
+        </is>
+      </c>
       <c r="K108" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5246,7 +5416,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5256,39 +5426,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>2020-09-09</t>
-        </is>
-      </c>
+      <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>3600.0</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
+          <t>339.999</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>340.0</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>-0.001</t>
+        </is>
+      </c>
       <c r="K109" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5296,7 +5466,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5308,30 +5478,30 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
           <t>2020-09-09</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="J110" t="inlineStr"/>
@@ -5354,36 +5524,32 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
           <t>2020-09-09</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>17952.0</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
@@ -5392,7 +5558,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5404,32 +5570,24 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
           <t>2020-09-09</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+          <t>上海市青浦县徐泾乡工业公司</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
@@ -5438,7 +5596,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5450,36 +5608,32 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
           <t>2020-09-09</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
       <c r="D113" t="inlineStr">
         <is>
           <t>罗世兵</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
           <t>204.0</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>408.0</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
@@ -5488,7 +5642,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5500,32 +5654,24 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
           <t>2020-09-09</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+          <t>友升太平洋(美国)投资有限公司</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
@@ -5534,7 +5680,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5546,40 +5692,32 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>7000.0</t>
-        </is>
-      </c>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>1680.0</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>1020.0</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
@@ -5588,7 +5726,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5600,32 +5738,36 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr"/>
+          <t>上海泽升贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
+          <t>8976.0</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>17952.0</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
@@ -5634,7 +5776,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5646,30 +5788,30 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="J117" t="inlineStr"/>
@@ -5692,32 +5834,36 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
@@ -5726,7 +5872,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5738,40 +5884,32 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>720.0</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
@@ -5780,7 +5918,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5792,32 +5930,36 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
+          <t>罗世兵</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>29.7333</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>29.7333</t>
-        </is>
-      </c>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>408.0</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
@@ -5826,7 +5968,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5838,30 +5980,30 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="J121" t="inlineStr"/>
@@ -5884,37 +6026,33 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
+          <t>1020.0</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>360.0</t>
+          <t>2040.0</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -5948,20 +6086,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="J123" t="inlineStr"/>
@@ -5994,20 +6132,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -6040,20 +6178,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="J125" t="inlineStr"/>
@@ -6086,20 +6224,20 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J126" t="inlineStr"/>
@@ -6132,20 +6270,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J127" t="inlineStr"/>
@@ -6166,39 +6304,43 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr"/>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司 (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>8976.0</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>1680.0</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6206,7 +6348,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6216,39 +6358,35 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr"/>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6256,7 +6394,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6266,39 +6404,35 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr"/>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙) (认缴→存量)</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6306,7 +6440,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6316,39 +6450,35 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr"/>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>罗世兵 (认缴→存量)</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6356,7 +6486,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6366,39 +6496,43 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr"/>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6406,7 +6540,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6416,39 +6550,35 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr"/>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6456,7 +6586,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6466,39 +6596,35 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr"/>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙) (认缴→存量)</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6506,7 +6632,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6642,11 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr"/>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C135" t="inlineStr">
         <is>
           <t>2022-12-19</t>
@@ -6524,31 +6654,31 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙) (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>720.0</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6556,7 +6686,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6569,29 +6699,29 @@
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙) (认缴→存量)</t>
+          <t>上海泽升贸易有限公司 (认缴→存量)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -6619,29 +6749,29 @@
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙) (认缴→存量)</t>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -6669,29 +6799,29 @@
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙) (认缴→存量)</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -6719,29 +6849,29 @@
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙) (认缴→存量)</t>
+          <t>罗世兵 (认缴→存量)</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -6769,29 +6899,29 @@
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙) (认缴→存量)</t>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -6819,29 +6949,29 @@
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -6869,29 +6999,29 @@
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -6924,24 +7054,24 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司 (认缴→存量)</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -6974,24 +7104,24 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙) (认缴→存量)</t>
+          <t>上海联炻企业管理中心(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -7013,30 +7143,42 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>高新同华</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K145" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7044,37 +7186,49 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>黄学英</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
-      <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K146" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7082,37 +7236,49 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>周乃鼎</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
-      <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K147" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7120,71 +7286,99 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>陆民</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K148" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr"/>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>华泰大健康一号</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr"/>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K149" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7192,37 +7386,49 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>复星惟盈</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K150" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7230,37 +7436,49 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>国寿疌泉</t>
+          <t>深圳市达晨财智创业投资管理有限公司 (认缴→存量)</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K151" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7268,37 +7486,49 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>史建伟</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr"/>
-      <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K152" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7306,7 +7536,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
@@ -7328,7 +7558,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>黄学英/刘鸿雁</t>
+          <t>周乃鼎</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -7366,7 +7596,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>周金清</t>
+          <t>黄学英</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -7404,7 +7634,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Cheer Rise Consultants Limited</t>
+          <t>周金清</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -7420,7 +7650,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7672,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>苏州贤达</t>
+          <t>国寿疌泉</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -7465,22 +7695,22 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>陆民</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -7494,31 +7724,27 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>Cheer Rise Consultants Limited</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -7541,22 +7767,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+          <t>复星惟盈</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -7572,29 +7798,29 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
+          <t>高新同华</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -7610,29 +7836,29 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>苏州贤达</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -7648,29 +7874,29 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+          <t>黄学英/刘鸿雁</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -7693,22 +7919,22 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>华泰大健康一号</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -7731,22 +7957,22 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>深圳中证投资有限责任公司</t>
+          <t>史建伟</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -7784,7 +8010,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>厦门富凯海创投资管理有限责任公司</t>
+          <t>深圳中证投资有限责任公司</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -7812,17 +8038,17 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
           <t>2015-07-09</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -7838,7 +8064,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7850,17 +8076,17 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
           <t>2015-07-09</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -7876,7 +8102,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7888,25 +8114,21 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
           <t>2015-07-09</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
@@ -7916,7 +8138,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr"/>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -7926,17 +8152,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
           <t>2015-07-09</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -7952,7 +8178,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7964,17 +8190,17 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2015-01</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>厦门富凯海创投资管理有限责任公司</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -8002,17 +8228,17 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2015-01</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -8028,7 +8254,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8040,17 +8266,17 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2015-01</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
+          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -8066,7 +8292,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8078,17 +8304,17 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2015-01</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -8116,21 +8342,25 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
           <t>2020-02-26</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>2023-03-24</t>
-        </is>
-      </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr"/>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
@@ -8140,51 +8370,35 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L174" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr"/>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>盛祎等15名自然人</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr"/>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>321.5</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>1739.315</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>1723.09</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>16.225</t>
-        </is>
-      </c>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -8192,29 +8406,29 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.9%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
@@ -8237,22 +8451,22 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>盛祎</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -8268,29 +8482,29 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>朱绶青</t>
+          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -8306,29 +8520,29 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -8344,29 +8558,29 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -8382,37 +8596,33 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>吴功友(王金林代持)</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
+      <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr"/>
@@ -8431,30 +8641,26 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>四方股份</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>1200.0</t>
-        </is>
-      </c>
+      <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
@@ -8473,34 +8679,42 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>2016-12-14</t>
-        </is>
-      </c>
+          <t>920100_三协电机</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>牛威(罗永红代持)</t>
+          <t>盛祎等15名自然人</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr"/>
-      <c r="H183" t="inlineStr"/>
-      <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>321.5</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>1739.315</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>1723.09</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>16.225</t>
+        </is>
+      </c>
       <c r="K183" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -8508,44 +8722,36 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.9%</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>920100_三协电机</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2002-11-07</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-08-09</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>幸福二期</t>
+          <t>朱绶青</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr"/>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
+      <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr"/>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
+      <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
@@ -8554,37 +8760,33 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>920100_三协电机</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2002-11-07</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-08-09</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>盛祎</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr"/>
@@ -8603,37 +8805,29 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>920100_三协电机</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2002-11-07</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-08-09</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>策星九天</t>
+          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
+      <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr"/>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
+      <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
@@ -8654,32 +8848,28 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司</t>
+          <t>四方股份</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr"/>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr"/>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+      <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr">
         <is>
@@ -8688,7 +8878,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8700,23 +8890,23 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>吴功友(王金林代持)</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>400.0</t>
         </is>
       </c>
       <c r="G188" t="inlineStr"/>
@@ -8742,32 +8932,24 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>策星揽月</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr"/>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
+      <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
+      <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
         <is>
@@ -8788,32 +8970,24 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>幸福一期</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
+      <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr"/>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
+      <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
         <is>
@@ -8834,32 +9008,28 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>策星银河</t>
+          <t>牛威(罗永红代持)</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr"/>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr"/>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+      <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
         <is>
@@ -8868,7 +9038,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8890,22 +9060,18 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>策星逐日</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
+      <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
@@ -8914,7 +9080,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8924,7 +9090,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr"/>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C193" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -8932,31 +9102,23 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司 (认缴→存量)</t>
+          <t>策星揽月</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr">
         <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr">
         <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -8964,7 +9126,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8974,7 +9136,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr"/>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C194" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -8982,7 +9148,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>策星九天 (认缴→存量)</t>
+          <t>策星九天</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
@@ -8992,21 +9158,13 @@
           <t>2345.0781</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr">
         <is>
           <t>2345.0781</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -9014,7 +9172,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9024,7 +9182,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr"/>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C195" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -9032,31 +9194,23 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>幸福一期 (认缴→存量)</t>
+          <t>幸福二期</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr">
         <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -9064,7 +9218,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9074,7 +9228,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr"/>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C196" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -9082,31 +9240,23 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>策星揽月 (认缴→存量)</t>
+          <t>幸福一期</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr">
         <is>
-          <t>412.5</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr">
         <is>
-          <t>412.5</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -9114,7 +9264,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9124,7 +9274,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr"/>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C197" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -9132,31 +9286,23 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>幸福二期 (认缴→存量)</t>
+          <t>中科星图股份有限公司</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr">
         <is>
-          <t>300.0</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
-          <t>300.0</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -9164,7 +9310,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9174,7 +9320,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr"/>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C198" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -9182,31 +9332,23 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>策星银河 (认缴→存量)</t>
+          <t>策星逐日</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
-          <t>279.0</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
-          <t>279.0</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -9214,7 +9356,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9366,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr"/>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C199" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -9232,31 +9378,19 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>策星逐日 (认缴→存量)</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
-      <c r="F199" t="inlineStr"/>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr">
+      <c r="F199" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -9264,35 +9398,431 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>策星银河</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr"/>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>中科星图股份有限公司 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
           <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="3" t="inlineStr">
-        <is>
-          <t>认缴流量: 14 条</t>
-        </is>
-      </c>
-    </row>
     <row r="202">
-      <c r="A202" s="3" t="inlineStr">
-        <is>
-          <t>股权存量: 14 条</t>
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr"/>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>策星九天 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>生成时间: 2026-06-12T14:44:15.889505</t>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr"/>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>幸福一期 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr"/>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>策星揽月 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr"/>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>幸福二期 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr"/>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>策星银河 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr"/>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>策星逐日 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
+          <t>认缴流量: 14 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>股权存量: 14 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>生成时间: 2026-06-12T15:16:11.078078</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A22:L22"/>
+    <mergeCell ref="A30:L30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/week2_excel/688775_影石创新_三表抽取.xlsx
+++ b/outputs/week2_excel/688775_影石创新_三表抽取.xlsx
@@ -2400,7 +2400,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>孙国敏</t>
+          <t>张松满</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -2418,11 +2418,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2442,7 +2438,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>张松满</t>
+          <t>孙国敏</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -2460,7 +2456,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2480,11 +2480,15 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>深圳市云汉电子有限公司</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -2496,7 +2500,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2518,15 +2522,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>深圳市云汉电子有限公司</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2982,15 +2982,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
@@ -3002,7 +2998,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3020,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -3040,7 +3036,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3058,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -3078,7 +3074,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3096,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -3116,7 +3112,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3134,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -3154,7 +3150,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3176,11 +3172,15 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -3556,7 +3556,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3632,13 +3632,13 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1000.0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -3674,13 +3674,13 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>7412.0</t>
+          <t>1584.0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -3716,13 +3716,13 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -3758,13 +3758,13 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -3800,13 +3800,13 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -3880,13 +3880,13 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1584.0</t>
+          <t>7412.0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -3960,15 +3960,11 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>中小企业发展基金（深圳有限合伙）</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
+      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
@@ -3980,7 +3976,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4002,11 +3998,15 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>中小企业发展基金（深圳有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4078,15 +4078,11 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>昆山谷捷金属制品有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
@@ -4098,7 +4094,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4120,11 +4116,15 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>昆山谷捷金属制品有限公司</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4336,7 +4336,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -4488,15 +4488,11 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>1153.0</t>
-        </is>
-      </c>
+      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
@@ -4508,7 +4504,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4572,11 +4568,15 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>1153.0</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4648,11 +4648,15 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2124.81</t>
+        </is>
+      </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
@@ -4662,11 +4666,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4762,15 +4762,11 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2124.81</t>
-        </is>
-      </c>
+      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
@@ -4780,7 +4776,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5488,14 +5488,22 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>友升太平洋(美国)投资有限公司</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
@@ -5504,7 +5512,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5526,20 +5534,20 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>罗世兵</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="J111" t="inlineStr"/>
@@ -5572,22 +5580,14 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+          <t>友升太平洋(美国)投资有限公司</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5618,22 +5618,14 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>上海市青浦县徐泾乡工业公司</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
@@ -5642,7 +5634,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5664,20 +5656,20 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="J114" t="inlineStr"/>
@@ -5710,14 +5702,22 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>上海市青浦县徐泾乡工业公司</t>
+          <t>罗世兵</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5748,22 +5748,26 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr"/>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
+          <t>1020.0</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>2040.0</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
@@ -5772,7 +5776,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5794,23 +5798,23 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>罗世兵</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>408.0</t>
+          <t>17952.0</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -5844,26 +5848,22 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>3600.0</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5894,26 +5894,22 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>17952.0</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
@@ -5922,7 +5918,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5944,22 +5940,26 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5990,26 +5990,22 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>2040.0</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
@@ -6018,7 +6014,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6040,22 +6036,26 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr"/>
+          <t>罗世兵</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>408.0</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6086,30 +6086,22 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>7000.0</t>
-        </is>
-      </c>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>1680.0</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
@@ -6118,7 +6110,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6286,22 +6278,30 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>10.1093</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>10.1093</t>
-        </is>
-      </c>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6332,30 +6332,22 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
@@ -6364,7 +6356,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6386,20 +6378,20 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="J129" t="inlineStr"/>
@@ -6432,20 +6424,20 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>51.959</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>51.959</t>
         </is>
       </c>
       <c r="J130" t="inlineStr"/>
@@ -6478,20 +6470,20 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="J131" t="inlineStr"/>
@@ -6524,20 +6516,20 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="J132" t="inlineStr"/>
@@ -6570,22 +6562,30 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>29.7333</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>29.7333</t>
-        </is>
-      </c>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>1680.0</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6616,20 +6616,20 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J134" t="inlineStr"/>
@@ -6662,20 +6662,20 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J135" t="inlineStr"/>
@@ -7558,7 +7558,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>黄学英</t>
+          <t>高新同华</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>华泰大健康一号</t>
+          <t>周乃鼎</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -7612,7 +7612,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>复星惟盈</t>
+          <t>Cheer Rise Consultants Limited</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>黄学英/刘鸿雁</t>
+          <t>黄学英</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>周乃鼎</t>
+          <t>周金清</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -7760,7 +7760,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7782,7 +7782,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>国寿疌泉</t>
+          <t>苏州贤达</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -7820,7 +7820,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>史建伟</t>
+          <t>国寿疌泉</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7858,7 +7858,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>高新同华</t>
+          <t>黄学英/刘鸿雁</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7896,7 +7896,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Cheer Rise Consultants Limited</t>
+          <t>复星惟盈</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7934,7 +7934,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>周金清</t>
+          <t>史建伟</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -7950,7 +7950,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7972,7 +7972,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>苏州贤达</t>
+          <t>华泰大健康一号</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -8010,7 +8010,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>深圳中证投资有限责任公司</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -8086,7 +8086,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>厦门富凯海创投资管理有限责任公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8124,7 +8124,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -8140,7 +8140,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+          <t>厦门富凯海创投资管理有限责任公司</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -8200,7 +8200,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -8238,7 +8238,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>深圳中证投资有限责任公司</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
@@ -8390,11 +8390,15 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
@@ -8404,11 +8408,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L175" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -8428,15 +8428,11 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
@@ -8446,7 +8442,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L176" t="inlineStr"/>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -8504,7 +8504,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -8580,7 +8580,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -8656,7 +8656,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
@@ -8744,7 +8744,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
+          <t>朱绶青</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8782,7 +8782,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>盛祎</t>
+          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
@@ -8798,7 +8798,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>朱绶青</t>
+          <t>盛祎</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
@@ -8942,11 +8942,15 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>四方股份</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
-      <c r="F189" t="inlineStr"/>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr"/>
@@ -8958,7 +8962,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8984,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
@@ -9018,15 +9022,11 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>四方股份</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>1200.0</t>
-        </is>
-      </c>
+      <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr"/>
@@ -9038,7 +9038,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9060,20 +9060,20 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>策星九天</t>
+          <t>幸福二期</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="J192" t="inlineStr"/>
@@ -9106,18 +9106,22 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>策星银河</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
       <c r="H193" t="inlineStr"/>
-      <c r="I193" t="inlineStr"/>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
@@ -9126,7 +9130,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9148,20 +9152,20 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>幸福一期</t>
+          <t>策星逐日</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="J194" t="inlineStr"/>
@@ -9194,20 +9198,20 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>策星逐日</t>
+          <t>策星揽月</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="J195" t="inlineStr"/>
@@ -9240,22 +9244,18 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>策星银河</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr"/>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr"/>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+      <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9286,20 +9286,20 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司</t>
+          <t>幸福一期</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr">
         <is>
-          <t>3825.0</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
-          <t>3825.0</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="J197" t="inlineStr"/>
@@ -9332,20 +9332,20 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>幸福二期</t>
+          <t>策星九天</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="J198" t="inlineStr"/>
@@ -9378,20 +9378,20 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>策星揽月</t>
+          <t>中科星图股份有限公司</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="J199" t="inlineStr"/>
@@ -9815,7 +9815,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>生成时间: 2026-06-12T16:09:12.748566</t>
+          <t>生成时间: 2026-06-12T16:30:01.183788</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/688775_影石创新_三表抽取.xlsx
+++ b/outputs/week2_excel/688775_影石创新_三表抽取.xlsx
@@ -1738,7 +1738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L143"/>
+  <dimension ref="A1:L211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2480,15 +2480,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>深圳市云汉电子有限公司</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -2500,7 +2496,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2518,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -2560,11 +2556,15 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>深圳市云汉电子有限公司</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3096,15 +3096,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
@@ -3138,11 +3134,15 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -3556,7 +3556,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -3632,13 +3632,13 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -3674,15 +3674,11 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>7412.0</t>
-        </is>
-      </c>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
@@ -3694,7 +3690,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3716,13 +3712,13 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>1000.0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -3758,13 +3754,13 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>1584.0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -3800,11 +3796,15 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3838,13 +3838,13 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1584.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -3880,13 +3880,13 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>7412.0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -3922,15 +3922,11 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -3942,7 +3938,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3964,11 +3960,15 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>中小企业发展基金（深圳有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
+          <t>中小企业发展基金（深圳有限合伙）</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -4078,11 +4078,15 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>昆山谷捷金属制品有限公司</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
@@ -4094,7 +4098,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4120,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -4154,15 +4158,11 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>昆山谷捷金属制品有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4196,7 +4196,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -4298,7 +4298,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4336,7 +4336,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -4488,11 +4488,15 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>10377.0</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
@@ -4504,7 +4508,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4526,15 +4530,11 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>1153.0</t>
-        </is>
-      </c>
+      <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4568,13 +4568,13 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>10377.0</t>
+          <t>1153.0</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -4610,11 +4610,15 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2124.81</t>
+        </is>
+      </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
@@ -4624,11 +4628,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -4724,15 +4724,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2124.81</t>
-        </is>
-      </c>
+      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
@@ -4742,7 +4738,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -4823,30 +4823,42 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>6999.972</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>-0.028</t>
+        </is>
+      </c>
       <c r="K97" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4854,37 +4866,49 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>2999.988</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>-0.012</t>
+        </is>
+      </c>
       <c r="K98" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4892,37 +4916,49 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>1499.994</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>-0.006</t>
+        </is>
+      </c>
       <c r="K99" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4930,37 +4966,49 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>厦门富凯海创投资管理有限责任公司</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>10000.0027</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>0.0027</t>
+        </is>
+      </c>
       <c r="K100" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4968,37 +5016,49 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>10000.0027</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>0.0027</t>
+        </is>
+      </c>
       <c r="K101" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5006,37 +5066,49 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>5000.0031</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>0.0031</t>
+        </is>
+      </c>
       <c r="K102" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5044,37 +5116,49 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>深圳中证投资有限责任公司</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>3000.0012</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>0.0012</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5082,37 +5166,49 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2912.5034</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2912.5</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>0.0034</t>
+        </is>
+      </c>
       <c r="K104" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5120,37 +5216,49 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2000.0019</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>2000.0</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>0.0019</t>
+        </is>
+      </c>
       <c r="K105" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5158,75 +5266,99 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>1747.5007</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>1747.5</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>0.0007</t>
+        </is>
+      </c>
       <c r="K106" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>price×shares vs amount diff=0.0%</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>999.9993</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>-0.0007</t>
+        </is>
+      </c>
       <c r="K107" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5234,37 +5366,49 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>999.9993</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>-0.0007</t>
+        </is>
+      </c>
       <c r="K108" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5272,37 +5416,49 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>339.999</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>340.0</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>-0.001</t>
+        </is>
+      </c>
       <c r="K109" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5310,29 +5466,29 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>上海市青浦县徐泾乡工业公司</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
@@ -5355,29 +5511,37 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
@@ -5386,36 +5550,44 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
@@ -5424,36 +5596,44 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
@@ -5469,22 +5649,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>友升太平洋(美国)投资有限公司</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
@@ -5507,42 +5687,38 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr"/>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>盛祎等15名自然人</t>
+          <t>罗世兵</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>321.5</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>1739.315</t>
-        </is>
-      </c>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
-          <t>1723.09</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>16.225</t>
-        </is>
-      </c>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5550,36 +5726,44 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.9%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
@@ -5595,29 +5779,37 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>盛祎</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
       <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
@@ -5626,35 +5818,47 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>朱绶青</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
@@ -5671,33 +5875,37 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>四方股份</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>1200.0</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
       <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
@@ -5706,35 +5914,47 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>牛威</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
+          <t>上海泽升贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>17952.0</t>
+        </is>
+      </c>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
@@ -5744,35 +5964,47 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>吴功友</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr"/>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2040.0</t>
+        </is>
+      </c>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
@@ -5782,39 +6014,47 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>牛威(罗永红代持)</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
+          <t>罗世兵</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>408.0</t>
+        </is>
+      </c>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
@@ -5831,33 +6071,37 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>吴功友(王金林代持)</t>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
       <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
@@ -5866,42 +6110,42 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>策星银河</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -5919,33 +6163,37 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
       <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
@@ -5954,42 +6202,42 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>幸福二期</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J126" t="inlineStr"/>
@@ -6007,37 +6255,45 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>策星揽月</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>412.5</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
@@ -6046,44 +6302,52 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>幸福一期</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>1680.0</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
@@ -6092,42 +6356,42 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>策星九天</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="J129" t="inlineStr"/>
@@ -6145,33 +6409,37 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
       <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
@@ -6180,42 +6448,42 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>策星逐日</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="J131" t="inlineStr"/>
@@ -6233,37 +6501,45 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>720.0</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
@@ -6272,49 +6548,45 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr"/>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司 (认缴→存量)</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6322,49 +6594,45 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr"/>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>策星九天 (认缴→存量)</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6372,49 +6640,45 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr"/>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>幸福一期 (认缴→存量)</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6422,42 +6686,42 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>策星揽月 (认缴→存量)</t>
+          <t>上海泽升贸易有限公司 (认缴→存量)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -6479,35 +6743,35 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>幸福二期 (认缴→存量)</t>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -6529,35 +6793,35 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>策星银河 (认缴→存量)</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -6579,35 +6843,35 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>策星逐日 (认缴→存量)</t>
+          <t>罗世兵 (认缴→存量)</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -6626,24 +6890,2932 @@
         </is>
       </c>
     </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
     <row r="141">
-      <c r="A141" s="3" t="inlineStr">
-        <is>
-          <t>认缴流量: 14 条</t>
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="3" t="inlineStr">
-        <is>
-          <t>股权存量: 14 条</t>
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>上海骁墨信息技术服务中心(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>生成时间: 2026-06-12T17:00:58.845054</t>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>上海联炻企业管理中心(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>安吉璞颉企业管理合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>上海杉创智至创业投资合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>深圳市达晨财智创业投资管理有限公司 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Cheer Rise Consultants Limited</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>复星惟盈</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>苏州贤达</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>黄学英</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>史建伟</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>周金清</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>周乃鼎</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>华泰大健康一号</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>高新同华</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>陆民</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>黄学英/刘鸿雁</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>EARN ACE LIMITED</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>深圳中证投资有限责任公司</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>香港迅雷有限公司</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>北京岚锋创视网络科技有限公司</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>QM101 Limited</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>厦门富凯海创投资管理有限责任公司</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>QM101 Limited</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>EARN ACE LIMITED</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>香港迅雷有限公司</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>北京岚锋创视网络科技有限公司</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>2023-03-24</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>2023-03-24</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>QM101 Limited</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>2023-03-24</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>EARN ACE LIMITED</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>2023-03-24</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>香港迅雷有限公司</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>2023-03-24</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>北京岚锋创视网络科技有限公司</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>920100_三协电机</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>盛祎等15名自然人</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>321.5</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>1739.315</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>1723.09</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>16.225</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>price×shares vs amount diff=0.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>920100_三协电机</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2002-11-07</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>盛祎</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>920100_三协电机</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2002-11-07</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>920100_三协电机</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2002-11-07</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>朱绶青</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>四方股份</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>吴功友(王金林代持)</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>牛威</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>吴功友</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>牛威(罗永红代持)</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>策星九天</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>幸福二期</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>策星逐日</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>牛威</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>吴功友</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>中科星图股份有限公司</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>幸福一期</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>策星揽月</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>策星银河</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr"/>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>中科星图股份有限公司 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr"/>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>策星九天 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr"/>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>幸福一期 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr"/>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>策星揽月 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr"/>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>幸福二期 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr"/>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>策星银河 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr"/>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>策星逐日 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
+          <t>认缴流量: 14 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>股权存量: 14 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>生成时间: 2026-06-12T17:05:42.726772</t>
         </is>
       </c>
     </row>
